--- a/results/final_20260514_v2_summary/HumanPseAAC_PartialAbstention_summary.xlsx
+++ b/results/final_20260514_v2_summary/HumanPseAAC_PartialAbstention_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:BU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,100 +476,320 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>afrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>afrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>arec__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>arec__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>arec__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>arec__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>f1_pa__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy_pa__0.3</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mfrd_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.0</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.1</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.2</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall_pa__0.3</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>rec__0.0</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>rec__0.1</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>rec__0.2</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>rec__0.3</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.0</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.1</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.2</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>subset0_1_pa__0.3</t>
         </is>
@@ -623,100 +843,320 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>0.5148±0.0559</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5105±0.0737</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.4383±0.1031</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.4310±0.0662</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.9823±0.0009</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.9810±0.0018</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.9766±0.0027</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.9620±0.0050</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5645±0.0294</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.5360±0.0269</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.4783±0.0273</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.3578±0.0234</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5551±0.0242</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5503±0.0245</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5310±0.0318</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.4549±0.0256</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
         <is>
           <t>0.5560±0.0266</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5370±0.0255</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>0.4927±0.0275</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.3842±0.0229</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>0.8868±0.0094</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>0.8597±0.0122</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.7965±0.0142</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.6802±0.0153</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5482±0.0265</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5253±0.0254</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.4729±0.0261</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.3552±0.0235</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.1959±0.0161</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.2166±0.0191</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.2169±0.0232</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.1935±0.0205</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.2078±0.0357</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.2015±0.0305</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.1753±0.0235</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.1355±0.0151</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.2092±0.0077</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.2563±0.0209</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.3076±0.0320</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.3836±0.0545</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.9329±0.0346</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.6329±0.0230</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>0.6299±0.0215</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.5932±0.0263</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.4593±0.0257</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>0.5640±0.0306</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>0.5235±0.0256</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.4544±0.0257</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.3149±0.0220</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.7219±0.0147</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.7921±0.0241</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.8556±0.0327</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.8506±0.0262</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>0.8242±0.0087</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.7960±0.0184</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.7469±0.0237</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>0.6551±0.0370</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>0.5252±0.0266</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.4911±0.0267</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.4177±0.0256</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.2807±0.0287</t>
         </is>
@@ -770,100 +1210,320 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>0.5148±0.0557</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.5085±0.0741</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.4394±0.1030</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.4320±0.0660</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.9823±0.0009</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.9809±0.0018</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.9765±0.0027</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.9617±0.0050</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.5645±0.0294</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.5359±0.0273</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.4775±0.0262</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.3570±0.0236</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.5560±0.0241</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.5510±0.0249</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.5318±0.0317</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.4559±0.0251</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0.5564±0.0265</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.5372±0.0259</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>0.4923±0.0267</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.3837±0.0229</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>0.8868±0.0093</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>0.8596±0.0122</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.7954±0.0140</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6779±0.0155</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.5483±0.0265</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.5253±0.0258</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.4722±0.0251</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.3544±0.0236</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.1958±0.0159</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.2187±0.0213</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.2163±0.0227</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.1931±0.0200</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.2076±0.0357</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.2043±0.0339</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.1743±0.0230</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.1349±0.0148</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.2093±0.0076</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.2583±0.0211</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.3081±0.0315</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.3852±0.0535</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.9320±0.0333</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6333±0.0228</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>0.6300±0.0216</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.5922±0.0258</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.4581±0.0256</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>0.5639±0.0307</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0.5231±0.0257</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.4528±0.0251</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.3135±0.0219</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.7230±0.0134</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.7931±0.0236</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.8573±0.0328</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.8526±0.0254</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>0.8239±0.0090</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>0.7957±0.0184</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.7463±0.0233</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>0.6545±0.0369</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>0.5243±0.0268</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.4904±0.0268</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.4161±0.0246</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.2795±0.0285</t>
         </is>
@@ -917,100 +1577,320 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>0.5148±0.0559</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.5113±0.0744</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.4387±0.1026</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.4307±0.0656</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.9823±0.0009</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.9809±0.0018</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.9766±0.0028</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.9619±0.0050</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.5645±0.0294</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.5358±0.0273</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.4781±0.0274</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0.3580±0.0235</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.5551±0.0242</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.5497±0.0247</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.5302±0.0319</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.4547±0.0262</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.5560±0.0266</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.5367±0.0258</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>0.4923±0.0277</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>0.3843±0.0231</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>0.8868±0.0094</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>0.8595±0.0124</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>0.7963±0.0144</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>0.6801±0.0154</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.5482±0.0265</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.5251±0.0258</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.4727±0.0262</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.3553±0.0236</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>0.1959±0.0161</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>0.2163±0.0193</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>0.2165±0.0230</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.1933±0.0205</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.2078±0.0357</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.2014±0.0305</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.1752±0.0235</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.1353±0.0151</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.2092±0.0077</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.2556±0.0213</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.3065±0.0313</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.3853±0.0584</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.9325±0.0352</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.6329±0.0230</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>0.6295±0.0219</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.5926±0.0265</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.4591±0.0259</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0.5640±0.0306</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>0.5232±0.0260</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>0.4542±0.0260</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.3149±0.0220</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.7219±0.0147</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>0.7912±0.0246</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.8540±0.0321</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.8491±0.0275</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
         <is>
           <t>0.8242±0.0087</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>0.7961±0.0187</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>0.7471±0.0236</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>0.6552±0.0370</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>0.5252±0.0266</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>0.4913±0.0272</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>0.4180±0.0256</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>0.2810±0.0286</t>
         </is>
@@ -1064,100 +1944,320 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>0.5148±0.0557</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.5092±0.0746</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.4396±0.1032</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.4319±0.0652</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.9823±0.0009</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.9809±0.0018</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.9765±0.0028</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.9616±0.0050</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.5645±0.0294</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.5356±0.0276</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.4774±0.0264</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.3572±0.0236</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.5560±0.0241</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.5505±0.0250</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.5313±0.0317</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.4561±0.0256</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.5564±0.0265</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.5368±0.0261</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>0.4921±0.0269</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>0.3839±0.0231</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>0.8868±0.0093</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>0.8594±0.0123</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>0.7951±0.0143</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>0.6777±0.0154</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.5483±0.0265</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.5250±0.0260</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.4721±0.0253</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.3545±0.0238</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0.1958±0.0159</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>0.2184±0.0215</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>0.2163±0.0231</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.1929±0.0199</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.2076±0.0357</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.2041±0.0339</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.1747±0.0236</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.1346±0.0147</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.2093±0.0076</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.2577±0.0214</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.3075±0.0320</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.3872±0.0572</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.9315±0.0337</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.6333±0.0228</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.6296±0.0220</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.5917±0.0262</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.4580±0.0256</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>0.5639±0.0307</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>0.5227±0.0260</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.4525±0.0255</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.3135±0.0218</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.7230±0.0134</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>0.7925±0.0239</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.8561±0.0325</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.8516±0.0264</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
         <is>
           <t>0.8239±0.0090</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>0.7957±0.0186</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>0.7464±0.0233</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>0.6545±0.0370</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>0.5243±0.0268</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>0.4903±0.0271</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>0.4164±0.0248</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>0.2795±0.0287</t>
         </is>
@@ -1211,100 +2311,320 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>0.5644±0.0686</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.5584±0.0835</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.6052±0.0626</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.5758±0.0624</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.9782±0.0011</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.9687±0.0021</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.9451±0.0049</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.8594±0.0079</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.5508±0.0270</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.5077±0.0178</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.4423±0.0191</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0.3044±0.0135</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.5360±0.0287</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.5185±0.0181</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.5217±0.0256</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.5629±0.0222</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.5382±0.0270</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.5040±0.0172</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.4620±0.0203</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>0.3710±0.0145</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>0.8731±0.0088</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>0.8505±0.0093</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>0.8119±0.0098</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>0.7297±0.0115</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.5278±0.0259</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.4858±0.0171</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.4264±0.0192</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.2950±0.0137</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0.1968±0.0253</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>0.2056±0.0202</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>0.2123±0.0186</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.1793±0.0130</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.2339±0.0534</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.2082±0.0369</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.1902±0.0263</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.1251±0.0094</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.2027±0.0168</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.2300±0.0211</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.2733±0.0177</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.3400±0.0359</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.9992±0.0021</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.9433±0.0235</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.6038±0.0228</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>0.5789±0.0157</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.5292±0.0174</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.3864±0.0154</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>0.5479±0.0233</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0.4956±0.0167</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>0.4167±0.0168</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.2640±0.0124</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.6726±0.0220</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.6965±0.0229</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.7256±0.0235</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.7211±0.0237</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
         <is>
           <t>0.7930±0.0123</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>0.6902±0.0200</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>0.4872±0.0339</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>0.1263±0.0212</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>0.4965±0.0245</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>0.4318±0.0204</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>0.3258±0.0203</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>0.1087±0.0168</t>
         </is>
@@ -1358,100 +2678,320 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.5741±0.0840</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.5592±0.0825</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.6031±0.0595</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.5619±0.0614</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.9782±0.0011</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.9677±0.0021</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.9424±0.0051</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.8466±0.0087</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0.5531±0.0250</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.5030±0.0170</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.4373±0.0176</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>0.2902±0.0133</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.5401±0.0251</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.5226±0.0185</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.5365±0.0246</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.5910±0.0212</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>0.5412±0.0244</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>0.5024±0.0168</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>0.4637±0.0184</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>0.3660±0.0141</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>0.8745±0.0072</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>0.8484±0.0084</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>0.8083±0.0095</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>0.7138±0.0118</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.5302±0.0240</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.4817±0.0166</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.4231±0.0173</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.2834±0.0131</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>0.2005±0.0211</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>0.2070±0.0202</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>0.2140±0.0173</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.1792±0.0106</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.2325±0.0500</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.2114±0.0405</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.1859±0.0238</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.1224±0.0080</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.2070±0.0138</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.2334±0.0204</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.2827±0.0179</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.3635±0.0353</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.9993±0.0020</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.9306±0.0284</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.6071±0.0193</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>0.5762±0.0149</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.5285±0.0157</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.3793±0.0148</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>0.5492±0.0210</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>0.4891±0.0160</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>0.4104±0.0151</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.2541±0.0122</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.6788±0.0167</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>0.7018±0.0223</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>0.7428±0.0229</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.7481±0.0176</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
         <is>
           <t>0.7914±0.0140</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>0.6795±0.0198</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>0.4661±0.0364</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>0.1021±0.0174</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>0.4975±0.0244</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>0.4207±0.0205</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>0.3090±0.0203</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>0.0869±0.0140</t>
         </is>
@@ -1505,100 +3045,320 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>0.5657±0.0681</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.5569±0.0791</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.6039±0.0641</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.5748±0.0633</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.9783±0.0011</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.9691±0.0021</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.9454±0.0049</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.8599±0.0076</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.5511±0.0274</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.5086±0.0182</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>0.4423±0.0191</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>0.3052±0.0137</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.5358±0.0292</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.5177±0.0183</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.5189±0.0249</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.5590±0.0218</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>0.5382±0.0274</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>0.5044±0.0173</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>0.4611±0.0200</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>0.3707±0.0144</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>0.8729±0.0088</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>0.8509±0.0094</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>0.8118±0.0098</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>0.7300±0.0117</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.5275±0.0263</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.4865±0.0168</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.4261±0.0190</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.2955±0.0136</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>0.1950±0.0255</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>0.2057±0.0215</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0.2123±0.0187</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>0.1794±0.0131</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.2321±0.0528</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.2093±0.0379</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.1907±0.0264</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.1255±0.0095</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.2009±0.0174</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.2289±0.0210</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.2723±0.0176</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.3381±0.0357</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.9995±0.0017</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.9412±0.0248</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>0.6025±0.0239</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>0.5792±0.0164</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.5285±0.0172</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.3858±0.0154</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>0.5478±0.0236</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>0.4969±0.0177</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>0.4173±0.0166</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>0.2641±0.0127</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>0.6694±0.0242</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>0.6947±0.0233</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>0.7211±0.0231</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.7164±0.0223</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
         <is>
           <t>0.7943±0.0123</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>0.6936±0.0196</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>0.4890±0.0344</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>0.1288±0.0207</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>0.4957±0.0246</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>0.4336±0.0188</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>0.3270±0.0202</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>0.1110±0.0165</t>
         </is>
@@ -1652,100 +3412,320 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>0.5619±0.0837</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.5590±0.0823</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.6109±0.0648</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.5607±0.0593</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.9779±0.0011</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.9677±0.0022</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.9423±0.0051</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.8469±0.0089</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0.5506±0.0251</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.5031±0.0184</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.4363±0.0179</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>0.2905±0.0136</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.5376±0.0254</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.5228±0.0193</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.5349±0.0255</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.5902±0.0210</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0.5387±0.0247</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>0.5026±0.0179</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>0.4624±0.0188</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>0.3662±0.0140</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>0.8733±0.0074</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>0.8485±0.0080</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>0.8079±0.0094</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>0.7138±0.0121</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.5278±0.0244</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.4820±0.0182</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.4217±0.0176</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.2837±0.0133</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0.1990±0.0218</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>0.2078±0.0212</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0.2138±0.0174</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0.1797±0.0115</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.2319±0.0502</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.2121±0.0419</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.1860±0.0239</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.1229±0.0086</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.2053±0.0139</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.2342±0.0210</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.2818±0.0159</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.3634±0.0355</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.9990±0.0023</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.9297±0.0290</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>0.6045±0.0203</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>0.5767±0.0160</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.5277±0.0160</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.3796±0.0151</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>0.5468±0.0210</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>0.4892±0.0172</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.4100±0.0157</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>0.2545±0.0124</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>0.6760±0.0197</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.7029±0.0226</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>0.7410±0.0215</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.7473±0.0188</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
         <is>
           <t>0.7898±0.0138</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>0.6794±0.0209</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>0.4647±0.0366</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>0.1028±0.0176</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>0.4951±0.0251</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>0.4213±0.0231</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>0.3074±0.0214</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>0.0875±0.0145</t>
         </is>
